--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Livee</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -947,14 +947,11 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au88dn/</t>
@@ -995,7 +992,6 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
           <t>N</t>
@@ -1026,7 +1022,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au88dn/</t>
@@ -1124,17 +1119,14 @@
           <t>[WPL] Create Request</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
+          <t>www.lg.com/x</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1172,7 +1164,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/it/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -1203,7 +1194,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>/it/notebook/gram-pro/17z90u-g-au78dn/</t>
@@ -1301,14 +1291,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/16z90tl-g-au75an/</t>
@@ -1349,7 +1336,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1482,14 +1468,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/16z90tl-g-au78an/</t>
@@ -1530,7 +1513,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>N</t>
@@ -1663,14 +1645,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/17z90tl-g-au78an/</t>
@@ -1711,7 +1690,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>N</t>
@@ -1844,14 +1822,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/17z90tl-g-au88an/</t>
@@ -1892,7 +1867,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
           <t>N</t>
@@ -2025,14 +1999,11 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au75dn/</t>
@@ -2073,7 +2044,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
           <t>N</t>
@@ -2104,7 +2074,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au75dn/</t>
@@ -2202,14 +2171,11 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au78dn/</t>
@@ -2250,7 +2216,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
           <t>N</t>
@@ -2281,7 +2246,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au78dn/</t>
@@ -2379,14 +2343,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-k-aub8an/</t>
@@ -2427,7 +2388,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -2560,14 +2520,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-h-au78an/</t>
@@ -2608,7 +2565,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -2741,14 +2697,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-books/16u55u-h-au75an/</t>
@@ -2789,7 +2742,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-book</t>
@@ -2922,14 +2874,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-books/15u50u-g-aa55an/</t>
@@ -2970,7 +2919,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
           <t>N</t>
@@ -3083,7 +3031,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -3099,15 +3046,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>라이브</t>
@@ -3143,7 +3086,6 @@
           <t>Ready to start production</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -3276,14 +3218,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/17z90u-g-au78an/</t>
@@ -3324,7 +3263,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3462,13 +3400,11 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
@@ -3509,7 +3445,6 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3540,7 +3475,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
@@ -3643,13 +3577,11 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
@@ -3690,7 +3622,6 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3721,7 +3652,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
@@ -3824,13 +3754,11 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-2-in-1/16t95tp-k-aa78gn/</t>
@@ -3871,7 +3799,6 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -3902,7 +3829,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-2-in-1/16t95tp-k-aa78gn/</t>
@@ -4005,13 +3931,11 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-2-in-1/16t95tp-k-ad8bgn/</t>
@@ -4052,7 +3976,6 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -4083,7 +4006,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-2-in-1/16t95tp-k-ad8bgn/</t>
@@ -4181,14 +4103,11 @@
           <t>[WPL] Request Clarification</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-k-aub8gn/</t>
@@ -4229,7 +4148,6 @@
           <t>Publication verified via lg.com sitemap</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -4265,7 +4183,6 @@
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>N</t>
@@ -4358,14 +4275,11 @@
           <t>[WPL] Request Clarification</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au78gn/</t>
@@ -4406,7 +4320,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -4554,7 +4467,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-para-creadores/14z95u-g-au88bn/</t>
@@ -4595,7 +4507,6 @@
           <t>Registered in PIM, NPI month 8</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram</t>
@@ -4626,7 +4537,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
           <t>/es/portatiles/gram/14z95u-g-au88bn/</t>
@@ -4704,7 +4614,6 @@
           <t>Client Review</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4725,14 +4634,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -4768,7 +4674,6 @@
           <t>Subsidiary: Spec assignment required</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
         <is>
           <t>N</t>
@@ -4881,7 +4786,6 @@
           <t>Client Review</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4902,14 +4806,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -4945,7 +4846,6 @@
           <t>Ready to start production</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
           <t>N</t>
@@ -5058,7 +4958,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -5079,14 +4978,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -5122,7 +5018,6 @@
           <t>Ready to start production</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -5260,13 +5155,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/17z90ub-h-au96bn/</t>
@@ -5307,7 +5200,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -5445,13 +5337,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/15u50u-g-aa55bn/</t>
@@ -5492,7 +5382,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr">
         <is>
           <t>N</t>
@@ -5605,7 +5494,6 @@
           <t>Clarify</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -5626,14 +5514,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -5669,7 +5554,6 @@
           <t>Subsidiary: Spec assignment required</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr">
         <is>
           <t>N</t>
@@ -5802,14 +5686,11 @@
           <t>[WPL] Client Review</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram-book/16u55u-g-au88bn/</t>
@@ -5850,7 +5731,6 @@
           <t>Registered in PIM, NPI month 8</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-book</t>
@@ -5979,14 +5859,11 @@
       <c r="N31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
@@ -6027,7 +5904,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/it/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -6058,7 +5934,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr">
         <is>
           <t>/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
@@ -6161,13 +6036,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14zb90s-g-aa55bn/</t>
@@ -6208,7 +6081,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
           <t>N</t>
@@ -6337,14 +6209,11 @@
       <c r="N33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/16zb90s-g-aa5dn/</t>
@@ -6385,7 +6254,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr">
         <is>
           <t>N</t>
@@ -6416,7 +6284,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr">
         <is>
           <t>/it/notebook/gram/16zb90s-g-aa5dn/</t>
@@ -6519,13 +6386,11 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/17z90tl-g-au75fn/</t>
@@ -6566,7 +6431,6 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr">
         <is>
           <t>N</t>
@@ -6597,7 +6461,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr">
         <is>
           <t>/fr/pc-portables/gram/17z90tl-g-au75fn/</t>
@@ -6700,13 +6563,11 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/17z90tl-g-au88fn/</t>
@@ -6747,7 +6608,6 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr">
         <is>
           <t>N</t>
@@ -6778,7 +6638,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr">
         <is>
           <t>/fr/pc-portables/gram/17z90tl-g-au88fn/</t>
@@ -6872,14 +6731,11 @@
       <c r="N36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/15u50u-g-ar53dn/</t>
@@ -6920,7 +6776,6 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr">
         <is>
           <t>N</t>
@@ -6951,7 +6806,6 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr">
         <is>
           <t>/it/notebook/gram/15u50u-g-ar53dn/</t>
@@ -7049,14 +6903,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
@@ -7097,7 +6948,6 @@
           <t>Publication verified via lg.com sitemap</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/au/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -7128,7 +6978,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr">
         <is>
           <t>/au/laptops/gram-pro/16z90u-g-au75ap/</t>
@@ -7171,7 +7020,6 @@
           <t>NPI</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7207,22 +7055,17 @@
           <t>etc</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="e">
         <v>#N/A</v>
       </c>
       <c r="N38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7258,7 +7101,6 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
           <t>N</t>
@@ -7274,7 +7116,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
           <t>0</t>
@@ -7285,8 +7126,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7324,7 +7163,6 @@
           <t>NPI</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7360,22 +7198,17 @@
           <t>etc</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="e">
         <v>#N/A</v>
       </c>
       <c r="N39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7411,7 +7244,6 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
           <t>N</t>
@@ -7427,7 +7259,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
           <t>0</t>
@@ -7438,8 +7269,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7477,7 +7306,6 @@
           <t>NPI</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7513,22 +7341,17 @@
           <t>etc</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="e">
         <v>#N/A</v>
       </c>
       <c r="N40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7564,7 +7387,6 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr">
         <is>
           <t>N</t>
@@ -7580,7 +7402,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
           <t>0</t>
@@ -7591,8 +7412,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7630,7 +7449,6 @@
           <t>MOD</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>NA</t>
@@ -7666,7 +7484,6 @@
           <t>live</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>WR2257506YW</t>
@@ -7677,14 +7494,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
@@ -7725,7 +7539,6 @@
           <t>Spec modification completed</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/ca_en/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -7756,7 +7569,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr">
         <is>
           <t>N</t>
@@ -7799,7 +7611,6 @@
           <t>MOD</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>NA</t>
@@ -7835,7 +7646,6 @@
           <t>live</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>WR2261186YW</t>
@@ -7846,14 +7656,11 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
@@ -7894,7 +7701,6 @@
           <t>Spec modification completed</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/ca_en/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -7925,7 +7731,6 @@
           <t>Need Assign</t>
         </is>
       </c>
-      <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr">
         <is>
           <t>N</t>
@@ -7968,7 +7773,6 @@
           <t>NPI</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -8004,21 +7808,17 @@
           <t>live</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="e">
         <v>#N/A</v>
       </c>
       <c r="N43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90ts-gu89j/</t>
@@ -8039,8 +7839,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
           <t>기게시(라이브)</t>
@@ -8056,18 +7854,6 @@
           <t>4/27 오픈 전 제품은 Readiness Check에 미노출</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8085,7 +7871,6 @@
           <t>NPI</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>EU</t>
@@ -8121,7 +7906,6 @@
           <t>live</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>WR2259877AK</t>
@@ -8137,13 +7921,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/16z90tl-g/</t>
@@ -8164,8 +7946,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
           <t>라이브 게시 확인 (AU88BN 페이지, 2026-07-23 사용자 확인)</t>
@@ -8181,18 +7961,6 @@
           <t>4/27 오픈 전 제품은 Readiness Check에 미노출</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AM44"/>
@@ -8412,7 +8180,6 @@
           <t>region</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8425,7 +8192,6 @@
           <t>sub</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8455,7 +8221,6 @@
           <t>model</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8519,7 +8284,6 @@
           <t>stageFallback</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8532,7 +8296,6 @@
           <t>pttId</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8545,7 +8308,6 @@
           <t>pttStatus</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8558,7 +8320,6 @@
           <t>targetStagingDate</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8571,7 +8332,6 @@
           <t>expectedLocalTargetDate</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8601,7 +8361,6 @@
           <t>stgUrl</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8648,7 +8407,6 @@
           <t>pdpStatus</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8695,7 +8453,6 @@
           <t>readinessTip</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8708,7 +8465,6 @@
           <t>detailKr</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8721,7 +8477,6 @@
           <t>detailEn</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8734,7 +8489,6 @@
           <t>statusTip</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Livee</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -947,11 +947,14 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au88dn/</t>
@@ -992,6 +995,7 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
           <t>N</t>
@@ -1022,6 +1026,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au88dn/</t>
@@ -1119,14 +1124,17 @@
           <t>[WPL] Create Request</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>www.lg.com/x</t>
+          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1164,6 +1172,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/it/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -1194,6 +1203,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>/it/notebook/gram-pro/17z90u-g-au78dn/</t>
@@ -1291,11 +1301,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/16z90tl-g-au75an/</t>
@@ -1336,6 +1349,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
           <t>N</t>
@@ -1468,11 +1482,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/16z90tl-g-au78an/</t>
@@ -1513,6 +1530,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>N</t>
@@ -1645,11 +1663,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/17z90tl-g-au78an/</t>
@@ -1690,6 +1711,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>N</t>
@@ -1822,11 +1844,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram/17z90tl-g-au88an/</t>
@@ -1867,6 +1892,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
           <t>N</t>
@@ -1999,11 +2025,14 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au75dn/</t>
@@ -2044,6 +2073,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
           <t>N</t>
@@ -2074,6 +2104,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au75dn/</t>
@@ -2171,11 +2202,14 @@
           <t>[WPL] Cancelled</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/17z90tl-g-au78dn/</t>
@@ -2216,6 +2250,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
           <t>N</t>
@@ -2246,6 +2281,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
           <t>/it/notebook/gram/17z90tl-g-au78dn/</t>
@@ -2343,11 +2379,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-k-aub8an/</t>
@@ -2388,6 +2427,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -2520,11 +2560,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-h-au78an/</t>
@@ -2565,6 +2608,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -2697,11 +2741,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-books/16u55u-h-au75an/</t>
@@ -2742,6 +2789,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-book</t>
@@ -2874,11 +2922,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-books/15u50u-g-aa55an/</t>
@@ -2919,6 +2970,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
           <t>N</t>
@@ -3031,6 +3083,7 @@
           <t>In Progress</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -3046,11 +3099,15 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>라이브</t>
@@ -3086,6 +3143,7 @@
           <t>Ready to start production</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -3218,11 +3276,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>https://www.lg.com/uk/laptops/gram-pro/17z90u-g-au78an/</t>
@@ -3263,6 +3324,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/uk/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3400,11 +3462,13 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
@@ -3445,6 +3509,7 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3475,6 +3540,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
@@ -3577,11 +3643,13 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
@@ -3622,6 +3690,7 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -3652,6 +3721,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
@@ -3754,11 +3824,13 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-2-in-1/16t95tp-k-aa78gn/</t>
@@ -3799,6 +3871,7 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -3829,6 +3902,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-2-in-1/16t95tp-k-aa78gn/</t>
@@ -3931,11 +4005,13 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-2-in-1/16t95tp-k-ad8bgn/</t>
@@ -3976,6 +4052,7 @@
           <t>Registered in PIM, NPI month 10</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro-2in1/16t95tp</t>
@@ -4006,6 +4083,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
           <t>/de/notebooks/gram-2-in-1/16t95tp-k-ad8bgn/</t>
@@ -4103,11 +4181,14 @@
           <t>[WPL] Request Clarification</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-k-aub8gn/</t>
@@ -4148,6 +4229,7 @@
           <t>Publication verified via lg.com sitemap</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -4183,6 +4265,7 @@
           <t>Confirmed</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>N</t>
@@ -4275,11 +4358,14 @@
           <t>[WPL] Request Clarification</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au78gn/</t>
@@ -4320,6 +4406,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/de/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -4467,6 +4554,7 @@
           <t>N</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/business/informatica/ordenadores/portatiles-para-creadores/14z95u-g-au88bn/</t>
@@ -4507,6 +4595,7 @@
           <t>Registered in PIM, NPI month 8</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram</t>
@@ -4537,6 +4626,7 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
           <t>/es/portatiles/gram/14z95u-g-au88bn/</t>
@@ -4614,6 +4704,7 @@
           <t>Client Review</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4634,11 +4725,14 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -4674,6 +4768,7 @@
           <t>Subsidiary: Spec assignment required</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
         <is>
           <t>N</t>
@@ -4786,6 +4881,7 @@
           <t>Client Review</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4806,11 +4902,14 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -4846,6 +4945,7 @@
           <t>Ready to start production</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
           <t>N</t>
@@ -4958,6 +5058,7 @@
           <t>In Progress</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4978,11 +5079,14 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -5018,6 +5122,7 @@
           <t>Ready to start production</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -5155,11 +5260,13 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/17z90ub-h-au96bn/</t>
@@ -5200,6 +5307,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -5337,11 +5445,13 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/laptops/gram/15u50u-g-aa55bn/</t>
@@ -5382,6 +5492,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr">
         <is>
           <t>N</t>
@@ -5494,6 +5605,7 @@
           <t>Clarify</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -5514,11 +5626,14 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
           <t>등록·미게시</t>
@@ -5554,6 +5669,7 @@
           <t>Subsidiary: Spec assignment required</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr">
         <is>
           <t>N</t>
@@ -5686,11 +5802,14 @@
           <t>[WPL] Client Review</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram-book/16u55u-g-au88bn/</t>
@@ -5731,6 +5850,7 @@
           <t>Registered in PIM, NPI month 8</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/es/ms/lgcom/2026/it/laptop/gram-book</t>
@@ -5859,11 +5979,14 @@
       <c r="N31" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
@@ -5904,6 +6027,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/it/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -5934,6 +6058,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr">
         <is>
           <t>/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
@@ -6036,11 +6161,13 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/14zb90s-g-aa55bn/</t>
@@ -6081,6 +6208,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
           <t>N</t>
@@ -6209,11 +6337,14 @@
       <c r="N33" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/16zb90s-g-aa5dn/</t>
@@ -6254,6 +6385,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr">
         <is>
           <t>N</t>
@@ -6284,6 +6416,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr">
         <is>
           <t>/it/notebook/gram/16zb90s-g-aa5dn/</t>
@@ -6386,11 +6519,13 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/17z90tl-g-au75fn/</t>
@@ -6431,6 +6566,7 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr">
         <is>
           <t>N</t>
@@ -6461,6 +6597,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr">
         <is>
           <t>/fr/pc-portables/gram/17z90tl-g-au75fn/</t>
@@ -6563,11 +6700,13 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>https://www.lg.com/fr/pc-portables/gram/17z90tl-g-au88fn/</t>
@@ -6608,6 +6747,7 @@
           <t>Registered in PIM, NPI month 7</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr">
         <is>
           <t>N</t>
@@ -6638,6 +6778,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr">
         <is>
           <t>/fr/pc-portables/gram/17z90tl-g-au88fn/</t>
@@ -6731,11 +6872,14 @@
       <c r="N36" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>https://www.lg.com/it/notebook/gram/15u50u-g-ar53dn/</t>
@@ -6776,6 +6920,7 @@
           <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr">
         <is>
           <t>N</t>
@@ -6806,6 +6951,7 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr">
         <is>
           <t>/it/notebook/gram/15u50u-g-ar53dn/</t>
@@ -6903,11 +7049,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
@@ -6948,6 +7097,7 @@
           <t>Publication verified via lg.com sitemap</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/au/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -6978,6 +7128,7 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr">
         <is>
           <t>/au/laptops/gram-pro/16z90u-g-au75ap/</t>
@@ -7020,6 +7171,7 @@
           <t>NPI</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7055,17 +7207,22 @@
           <t>etc</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="e">
         <v>#N/A</v>
       </c>
       <c r="N38" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7101,6 +7258,7 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
           <t>N</t>
@@ -7116,6 +7274,7 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
           <t>0</t>
@@ -7126,6 +7285,8 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7163,6 +7324,7 @@
           <t>NPI</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7198,17 +7360,22 @@
           <t>etc</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="e">
         <v>#N/A</v>
       </c>
       <c r="N39" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7244,6 +7411,7 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
           <t>N</t>
@@ -7259,6 +7427,7 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
           <t>0</t>
@@ -7269,6 +7438,8 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7306,6 +7477,7 @@
           <t>NPI</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7341,17 +7513,22 @@
           <t>etc</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="e">
         <v>#N/A</v>
       </c>
       <c r="N40" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
           <t>PIM 미등록</t>
@@ -7387,6 +7564,7 @@
           <t>Subsidiary: Spec check required</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr">
         <is>
           <t>N</t>
@@ -7402,6 +7580,7 @@
           <t>N</t>
         </is>
       </c>
+      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
           <t>0</t>
@@ -7412,6 +7591,8 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7449,6 +7630,7 @@
           <t>MOD</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>NA</t>
@@ -7484,6 +7666,7 @@
           <t>live</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>WR2257506YW</t>
@@ -7494,11 +7677,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
@@ -7539,6 +7725,7 @@
           <t>Spec modification completed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/ca_en/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -7569,6 +7756,7 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr">
         <is>
           <t>N</t>
@@ -7611,6 +7799,7 @@
           <t>MOD</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>NA</t>
@@ -7646,6 +7835,7 @@
           <t>live</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>WR2261186YW</t>
@@ -7656,11 +7846,14 @@
           <t>[WPL] Closed</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
@@ -7701,6 +7894,7 @@
           <t>Spec modification completed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
           <t>/content/dam/channel/wcms/1-channel/ca_en/ms/lgcom/2026/it/laptop/gram-pro</t>
@@ -7731,6 +7925,7 @@
           <t>Need Assign</t>
         </is>
       </c>
+      <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr">
         <is>
           <t>N</t>
@@ -7773,6 +7968,7 @@
           <t>NPI</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>SEA</t>
@@ -7808,17 +8004,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="e">
         <v>#N/A</v>
       </c>
       <c r="N43" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>https://www.lg.com/jp/mobile-pc/gram/16z90ts-gu89j/</t>
@@ -7839,6 +8039,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
           <t>기게시(라이브)</t>
@@ -7854,6 +8056,18 @@
           <t>4/27 오픈 전 제품은 Readiness Check에 미노출</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7871,6 +8085,7 @@
           <t>NPI</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>EU</t>
@@ -7906,6 +8121,7 @@
           <t>live</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>WR2259877AK</t>
@@ -7921,11 +8137,13 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>https://www.lg.com/es/portatiles/gram/16z90tl-g/</t>
@@ -7946,6 +8164,8 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
           <t>라이브 게시 확인 (AU88BN 페이지, 2026-07-23 사용자 확인)</t>
@@ -7961,6 +8181,18 @@
           <t>4/27 오픈 전 제품은 Readiness Check에 미노출</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AM44"/>
@@ -8180,6 +8412,7 @@
           <t>region</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8192,6 +8425,7 @@
           <t>sub</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8221,6 +8455,7 @@
           <t>model</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8284,6 +8519,7 @@
           <t>stageFallback</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8296,6 +8532,7 @@
           <t>pttId</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8308,6 +8545,7 @@
           <t>pttStatus</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8320,6 +8558,7 @@
           <t>targetStagingDate</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8332,6 +8571,7 @@
           <t>expectedLocalTargetDate</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8361,6 +8601,7 @@
           <t>stgUrl</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8407,6 +8648,7 @@
           <t>pdpStatus</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8453,6 +8695,7 @@
           <t>readinessTip</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8465,6 +8708,7 @@
           <t>detailKr</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8477,6 +8721,7 @@
           <t>detailEn</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8489,6 +8734,7 @@
           <t>statusTip</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:49</t>
+          <t>2026-10-06 09:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261002.xlsb</t>
+          <t>raw-data-20261003.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8316,6 +8316,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -5071,7 +5071,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>[WB] In progress</t>
+          <t>[QA] QA review</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:25</t>
+          <t>2026-10-07 14:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261003.xlsb</t>
+          <t>raw-data-20261007.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8290,7 +8290,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cms_merged_view_20260929_094746.csv</t>
+          <t>cms_merged_view_20261006_142004.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 14:44</t>
+          <t>2026-10-08 09:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261007.xlsb</t>
+          <t>raw-data-20261008.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cms_merged_view_20261006_142004.csv</t>
+          <t>cms_merged_view_20261007_165625.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -5071,7 +5071,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>[QA] QA review</t>
+          <t>[QA] Final Live Check</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:41</t>
+          <t>2026-10-14 15:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261008.xlsb</t>
+          <t>raw-data-20261014.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15</t>
+          <t>2026-10-15 10:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261014.xlsb</t>
+          <t>raw-data-20261015.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -7861,7 +7861,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>등록·미게시</t>
+          <t>라이브</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:24</t>
+          <t>2026-10-15 17:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cms_merged_view_20261007_165625.csv</t>
+          <t>cms_merged_view_20261015_171640.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>/it/small-medium-business/notebook/gram/17z90tl-g-au88dn/</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Not Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Spec Y · KF 6 · UFN ✓ · Need Assign · Confirmed · gp1</t>
+          <t>Spec Y · KF 6 · UFN ✓ · Assigned · Confirmed · gp1</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>법인 Spec Assign 필요</t>
+          <t>제작 착수 가능</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Subsidiary: Spec assignment required</t>
+          <t>Ready to start production</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Portátil 16" LG gram Pro 16ZD90U, Copilot+ PC, FreeOS, Intel® Core™ Ultra 7, 32 GB RAM , 512GB SSD,  Pantalla IPS (2560*1600), ligero, 1.239 g, 29.5  horas, AI, Negro carbón</t>
+          <t>Portátil 16" LG gram Pro 16ZD90U, FreeOS, Intel® Core™ Ultra 7, 32 GB RAM , 512GB SSD,  Pantalla IPS (2560*1600), ligero, 1.239 g, 29.5  horas, AI, Negro carbón</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Need Assign</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5055,10 +5055,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -5086,10 +5090,14 @@
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram-pro/17z90u-g-au88bn/</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>등록·미게시</t>
+          <t>라이브</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -5109,17 +5117,17 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Spec Y · KF 6 · UFN ✓ · SPEC Need Publish · Confirmed · gp1</t>
+          <t>Spec Y · KF 6 · UFN ✓ · Assigned · Confirmed · gp1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>제작 착수 가능</t>
+          <t>라이브 게시 확인 (실측 200, 2026-10-16)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Ready to start production</t>
+          <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr"/>
@@ -5150,7 +5158,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>SPEC Need Publish</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -5160,7 +5168,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>/es/portatiles/gram-pro/17z90u-g-au88bn/</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -5345,7 +5353,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>/es/laptops/gram/17z90ub-h-au96bn/</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5572,7 +5580,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5651,22 +5659,22 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Not Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Spec Y · KF 6 · UFN ✓ · Need Assign · Confirmed · gp1</t>
+          <t>Spec Y · KF 6 · UFN ✓ · Assigned · Confirmed · gp1</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>법인 Spec Assign 필요</t>
+          <t>제작 착수 가능</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Subsidiary: Spec assignment required</t>
+          <t>Ready to start production</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr"/>
@@ -5687,7 +5695,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Portátil 16" LG gramBook 16UD55U, Copilot+ PC, FreeOS, Ryzen AI 7 445 , 32 GB RAM , 512GB SSD, AMD Radeon™ Graphics , Pantalla IPS (1920*1200), ligero, 1.800 g, 26 horas, AI, Negro carbón</t>
+          <t>Portátil 16" LG gramBook 16UD55U, FreeOS, Ryzen AI 7 445 , 32 GB RAM , 512GB SSD, AMD Radeon™ Graphics , Pantalla IPS (1920*1200), ligero, 1.800 g, 26 horas, AI, Negro carbón</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -5697,7 +5705,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Need Assign</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -8239,7 +8247,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 17:00</t>
+          <t>2026-10-16 11:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8307,7 +8315,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Readiness_Check_AllLocales_20260922_113628.xlsx</t>
+          <t>Readiness_Check_AllLocales_20261016_105711.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:08</t>
+          <t>2026-10-19 09:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261015.xlsb</t>
+          <t>raw-data-20261018.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 09:09</t>
+          <t>2026-10-20 09:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261018.xlsb</t>
+          <t>raw-data-20261020.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -1121,7 +1121,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[WPL] Create Request</t>
+          <t>[WPL] Cancelled</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -4878,10 +4878,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Client Review</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>precheck</t>
@@ -4909,10 +4913,14 @@
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/laptops/gram/17z90tl-g-au88bn/</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>등록·미게시</t>
+          <t>라이브</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4937,12 +4945,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>제작 착수 가능</t>
+          <t>라이브 게시 확인 (실측 200, 2026-10-21)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Ready to start production</t>
+          <t>Publication verified (HTTP 200)</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
@@ -5075,7 +5083,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>[QA] Final Live Check</t>
+          <t>[WPL] Publishing Approve</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -6519,7 +6527,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>[WPL] Create Request</t>
+          <t>[WPL] Cancelled</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6700,7 +6708,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>[WPL] Create Request</t>
+          <t>[WPL] Cancelled</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -7700,7 +7708,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>라이브</t>
+          <t>PIM 미등록</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -7869,7 +7877,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>라이브</t>
+          <t>PIM 미등록</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -8247,7 +8255,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 09:34</t>
+          <t>2026-10-21 10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8281,7 +8289,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261020.xlsb</t>
+          <t>raw-data-20261021.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8298,7 +8306,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cms_merged_view_20261015_171640.csv</t>
+          <t>cms_merged_view_20261020_160355.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/it/_upload/IT_product_status.xlsx
+++ b/it/_upload/IT_product_status.xlsx
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:00</t>
+          <t>2026-10-22 10:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw-data-20261021.xlsb</t>
+          <t>raw-data-20261022.xlsb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
